--- a/docs/Decodifiche/3_dec_use_case.xlsx
+++ b/docs/Decodifiche/3_dec_use_case.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2058" uniqueCount="685">
   <si>
     <t>ID</t>
   </si>
@@ -1482,6 +1482,12 @@
   </si>
   <si>
     <t>Dichiarazione: Matrimonio con Rito Religioso Acattolico</t>
+  </si>
+  <si>
+    <t>323111</t>
+  </si>
+  <si>
+    <t>Matrimonio religioso tra cittadini stranieri residenti all'estero</t>
   </si>
   <si>
     <t>329999</t>
@@ -2119,7 +2125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G342"/>
+  <dimension ref="A1:G343"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="9.95703125" customWidth="true" bestFit="true"/>
@@ -6878,7 +6884,7 @@
         <v>491</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>8</v>
+        <v>331</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>9</v>
@@ -6907,7 +6913,7 @@
         <v>10</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>322</v>
+        <v>14</v>
       </c>
     </row>
     <row r="240">
@@ -6998,7 +7004,7 @@
         <v>503</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>504</v>
+        <v>8</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>9</v>
@@ -7012,13 +7018,13 @@
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B245" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="B245" s="2" t="s">
+      <c r="C245" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="C245" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>9</v>
@@ -7047,7 +7053,7 @@
         <v>10</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>14</v>
+        <v>322</v>
       </c>
     </row>
     <row r="247">
@@ -7178,10 +7184,10 @@
         <v>522</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>331</v>
+        <v>8</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>523</v>
+        <v>9</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>10</v>
@@ -7192,16 +7198,16 @@
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B254" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="B254" s="2" t="s">
+      <c r="C254" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D254" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D254" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>10</v>
@@ -7255,7 +7261,7 @@
         <v>530</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>393</v>
+        <v>531</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>8</v>
@@ -7267,15 +7273,15 @@
         <v>10</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>394</v>
+        <v>14</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>451</v>
+        <v>393</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>8</v>
@@ -7292,10 +7298,10 @@
     </row>
     <row r="259">
       <c r="A259" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>398</v>
+        <v>451</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>8</v>
@@ -7312,10 +7318,10 @@
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>8</v>
@@ -7332,13 +7338,13 @@
     </row>
     <row r="261">
       <c r="A261" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>406</v>
+        <v>8</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>9</v>
@@ -7352,13 +7358,13 @@
     </row>
     <row r="262">
       <c r="A262" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>331</v>
+        <v>406</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>9</v>
@@ -7372,13 +7378,13 @@
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>7</v>
+        <v>408</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>8</v>
+        <v>331</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>9</v>
@@ -7387,15 +7393,15 @@
         <v>10</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>11</v>
+        <v>394</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>538</v>
+        <v>7</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>8</v>
@@ -7407,7 +7413,7 @@
         <v>10</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="265">
@@ -7527,7 +7533,7 @@
         <v>10</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>322</v>
+        <v>14</v>
       </c>
     </row>
     <row r="271">
@@ -7598,7 +7604,7 @@
         <v>558</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>331</v>
+        <v>8</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>9</v>
@@ -7618,7 +7624,7 @@
         <v>560</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>8</v>
+        <v>331</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>9</v>
@@ -7647,7 +7653,7 @@
         <v>10</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>14</v>
+        <v>322</v>
       </c>
     </row>
     <row r="277">
@@ -7738,7 +7744,7 @@
         <v>572</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>331</v>
+        <v>8</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>9</v>
@@ -7758,7 +7764,7 @@
         <v>574</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>8</v>
+        <v>331</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>9</v>
@@ -7775,7 +7781,7 @@
         <v>575</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>393</v>
+        <v>576</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>8</v>
@@ -7787,15 +7793,15 @@
         <v>10</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>394</v>
+        <v>14</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>451</v>
+        <v>393</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>8</v>
@@ -7812,10 +7818,10 @@
     </row>
     <row r="285">
       <c r="A285" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>398</v>
+        <v>451</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>8</v>
@@ -7832,10 +7838,10 @@
     </row>
     <row r="286">
       <c r="A286" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>8</v>
@@ -7852,13 +7858,13 @@
     </row>
     <row r="287">
       <c r="A287" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>406</v>
+        <v>8</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>9</v>
@@ -7872,13 +7878,13 @@
     </row>
     <row r="288">
       <c r="A288" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>331</v>
+        <v>406</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>9</v>
@@ -7892,13 +7898,13 @@
     </row>
     <row r="289">
       <c r="A289" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>582</v>
+        <v>408</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>583</v>
+        <v>331</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>9</v>
@@ -7912,13 +7918,13 @@
     </row>
     <row r="290">
       <c r="A290" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B290" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="B290" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="C290" s="2" t="s">
-        <v>8</v>
+        <v>585</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>9</v>
@@ -7927,15 +7933,15 @@
         <v>10</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>11</v>
+        <v>394</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>586</v>
+        <v>7</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>8</v>
@@ -7947,7 +7953,7 @@
         <v>10</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="292">
@@ -8287,7 +8293,7 @@
         <v>10</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>322</v>
+        <v>14</v>
       </c>
     </row>
     <row r="309">
@@ -8818,7 +8824,7 @@
         <v>674</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>387</v>
+        <v>8</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>9</v>
@@ -8838,7 +8844,7 @@
         <v>676</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>8</v>
+        <v>387</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>9</v>
@@ -8855,7 +8861,7 @@
         <v>677</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>393</v>
+        <v>678</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>8</v>
@@ -8867,15 +8873,15 @@
         <v>10</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>394</v>
+        <v>322</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>451</v>
+        <v>393</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>8</v>
@@ -8892,10 +8898,10 @@
     </row>
     <row r="339">
       <c r="A339" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>398</v>
+        <v>451</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>8</v>
@@ -8912,10 +8918,10 @@
     </row>
     <row r="340">
       <c r="A340" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>8</v>
@@ -8932,13 +8938,13 @@
     </row>
     <row r="341">
       <c r="A341" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>406</v>
+        <v>8</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>9</v>
@@ -8952,21 +8958,41 @@
     </row>
     <row r="342">
       <c r="A342" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B342" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C342" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D342" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E342" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F342" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="B343" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="C342" s="2" t="s">
+      <c r="C343" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="D342" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E342" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F342" s="2" t="s">
+      <c r="D343" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E343" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F343" s="2" t="s">
         <v>394</v>
       </c>
     </row>

--- a/docs/Decodifiche/3_dec_use_case.xlsx
+++ b/docs/Decodifiche/3_dec_use_case.xlsx
@@ -7354,7 +7354,7 @@
         <v>10</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="252">
@@ -7394,7 +7394,7 @@
         <v>10</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="254">
@@ -8234,7 +8234,7 @@
         <v>10</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>10</v>
+        <v>326</v>
       </c>
     </row>
     <row r="296">
@@ -8594,7 +8594,7 @@
         <v>10</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="314">
